--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2266,49 +2266,49 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2758,7 +2758,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2816,42 +2816,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2868,7 +2868,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2919,49 +2919,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2978,7 +2978,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3029,42 +3029,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,14 +3369,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3584,11 +3584,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3605,7 +3629,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3623,7 +3647,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3666,7 +3690,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3676,14 +3700,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3701,7 +3725,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3740,35 +3764,11 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45813</v>
+        <v>44771</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2266,49 +2266,49 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2758,7 +2758,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2816,42 +2816,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2868,7 +2868,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2919,49 +2919,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2978,7 +2978,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3029,42 +3029,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>44771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,8 +3388,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3447,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,13 +3466,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3584,35 +3584,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3629,7 +3605,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3647,7 +3623,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3690,7 +3666,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3700,14 +3676,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44798</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3725,7 +3701,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3764,11 +3740,35 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44771</v>
+        <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2266,49 +2266,49 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,22 +2770,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2800,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2809,49 +2804,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2868,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2881,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2919,49 +2914,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2978,7 +2973,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,13 +2991,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3036,42 +3031,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3085,10 +3080,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3101,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3146,42 +3141,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3191,14 +3186,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,17 +3205,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,46 +3247,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44771</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,13 +3388,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3437,7 +3432,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3451,10 +3446,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3466,8 +3461,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3539,13 +3539,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3605,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3768,7 +3763,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3778,14 +3773,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45813</v>
+        <v>46225</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,8 +3792,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,21 +2238,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2263,59 +2268,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2325,14 +2330,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,25 +2349,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2374,59 +2374,59 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,14 +2665,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2699,49 +2704,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2756,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,17 +2775,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2807,39 +2817,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2863,7 +2873,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2956,7 +2966,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2970,10 +2980,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +3001,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3024,49 +3034,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3076,14 +3086,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,19 +3105,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3137,46 +3142,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,14 +3191,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,22 +3210,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,46 +3247,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,14 +3369,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44852</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44771</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3539,8 +3539,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3600,7 +3605,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3683,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3763,7 +3768,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3773,14 +3778,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46225</v>
+        <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3792,13 +3797,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,16 +2238,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2256,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2268,59 +2263,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2330,14 +2325,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,20 +2344,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2374,59 +2374,59 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,19 +2665,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2704,49 +2699,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2756,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,22 +2770,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2817,39 +2807,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -2873,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2966,7 +2956,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2980,10 +2970,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,13 +2991,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3034,49 +3024,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3086,14 +3076,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3105,14 +3095,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3142,46 +3137,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3191,14 +3186,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,17 +3205,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,39 +3247,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,14 +3369,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,8 +3388,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3447,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,13 +3466,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3527,7 +3527,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3662,11 +3662,35 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3680,10 +3704,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3701,7 +3725,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3740,30 +3764,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,17 +2770,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2804,49 +2809,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2863,7 +2868,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,13 +2886,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2921,42 +2926,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2973,7 +2978,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +2996,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3024,49 +3029,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3080,10 +3085,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3106,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3141,42 +3146,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,14 +3191,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,22 +3210,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,39 +3247,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,22 +2770,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2800,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2809,42 +2804,42 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -2868,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2973,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3066,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3085,10 +3080,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3101,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3139,49 +3134,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3191,14 +3186,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,17 +3205,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,39 +3247,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,13 +3388,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3454,7 +3449,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3510,7 +3505,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3520,14 +3515,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3545,7 +3540,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3588,7 +3583,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3623,7 +3618,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3662,35 +3657,11 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3707,7 +3678,7 @@
         <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3725,7 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3768,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3778,14 +3749,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45813</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,8 +3768,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3837,6 +3813,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,35 +2706,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
         <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2863,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2921,42 +2921,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2973,7 +2973,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3024,49 +3024,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3083,7 +3083,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3134,42 +3134,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45813</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,8 +3388,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3449,7 +3454,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3505,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3515,14 +3520,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3540,7 +3545,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3583,7 +3588,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3618,7 +3623,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3657,11 +3662,35 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3678,7 +3707,7 @@
         <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3696,7 +3725,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3739,7 +3768,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3749,14 +3778,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>45813</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3768,13 +3797,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3813,30 +3837,6 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,21 +2238,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2263,59 +2268,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2325,14 +2330,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,25 +2349,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2374,59 +2374,59 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,14 +2665,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2699,49 +2704,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2756,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,17 +2775,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2807,39 +2817,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2863,7 +2873,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2956,7 +2966,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2970,10 +2980,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +3001,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3024,49 +3034,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3076,14 +3086,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,19 +3105,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3137,46 +3142,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,14 +3191,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,22 +3210,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,46 +3247,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,13 +3388,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3454,7 +3449,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3510,7 +3505,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3527,7 +3522,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3545,7 +3540,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3588,7 +3583,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3623,7 +3618,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3662,35 +3657,11 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3704,10 +3675,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3725,7 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3764,11 +3735,35 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3782,10 +3777,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45813</v>
+        <v>44798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,8 +3792,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45415</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45415</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,16 +2238,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2256,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2268,59 +2263,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2330,14 +2325,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,20 +2344,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2374,59 +2374,59 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,19 +2665,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2704,49 +2699,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2756,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,22 +2770,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2817,39 +2807,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -2873,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2966,7 +2956,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2980,10 +2970,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,13 +2991,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3034,49 +3024,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3086,14 +3076,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3105,14 +3095,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3142,46 +3137,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3191,14 +3186,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,17 +3205,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,39 +3247,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,8 +3461,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3505,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3519,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3534,13 +3539,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3773,14 +3773,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2266,49 +2266,49 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,17 +2770,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2804,49 +2809,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2863,7 +2868,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,7 +2886,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2914,49 +2919,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2973,7 +2978,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +2996,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3031,42 +3036,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3080,10 +3085,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3106,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3141,42 +3146,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,14 +3191,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,22 +3210,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,39 +3247,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,13 +3461,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3505,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3520,14 +3515,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3539,8 +3534,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3661,7 +3661,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3735,35 +3735,11 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3777,10 +3753,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3798,7 +3774,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3837,6 +3813,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2266,49 +2266,49 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2601,35 +2601,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,19 +2770,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2809,49 +2804,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2868,7 +2863,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2881,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2919,49 +2914,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2978,7 +2973,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,13 +2991,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3036,42 +3031,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3085,10 +3080,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3101,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3146,42 +3141,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3191,14 +3186,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,17 +3205,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,46 +3247,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,8 +3315,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3364,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,14 +3374,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44852</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,7 +3394,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3442,14 +3447,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44771</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3462,7 +3467,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3505,7 +3510,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3519,10 +3524,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44798</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3534,13 +3539,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3661,7 +3661,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3735,11 +3735,35 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3753,10 +3777,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3774,7 +3798,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3813,30 +3837,6 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45894</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45076</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>45608</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>45211</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1827,283 +1827,283 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2160,56 +2160,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,21 +2238,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2263,59 +2268,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2325,14 +2330,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,25 +2349,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2374,59 +2374,59 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2443,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2496,42 +2496,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2601,42 +2601,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,8 +2665,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2699,10 +2704,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2710,38 +2715,38 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2751,14 +2756,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2770,8 +2775,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2807,39 +2817,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2863,7 +2873,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2956,7 +2966,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2970,10 +2980,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,13 +3001,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3024,49 +3034,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3076,14 +3086,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,19 +3105,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3137,46 +3142,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,14 +3191,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,22 +3210,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3247,46 +3247,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44798</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,13 +3315,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3364,7 +3359,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3374,14 +3369,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3394,7 +3389,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3437,7 +3432,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3447,14 +3442,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>44771</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3467,7 +3462,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3510,7 +3505,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3520,14 +3515,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44852</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3539,8 +3534,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3671,14 +3671,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3735,35 +3735,11 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3777,10 +3753,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3798,7 +3774,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3837,6 +3813,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 40110-2025</t>
+          <t>A 24264-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45894</v>
+        <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>21.4</v>
+        <v>7.3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,165 +638,21 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>16</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>32</v>
-      </c>
       <c r="T2" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="U2" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Rosetticka
-Brunpudrad nållav
-Fjällig taggsvamp s.str.
-Mindre poppelglasvinge
-Motaggsvamp
-Orange taggsvamp
-Rynkskinn
-Scharlakansvaxing
-Skarp dropptaggsvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vaddporing
-Vedtrappmossa
-Björksplintborre
-Brandticka
-Bronshjon
-Flagellkvastmossa
-Granbarkgnagare
-Grön sköldmossa
-Hasselticka
-Mindre märgborre
-Stubbspretmossa
-Thomsons trägnagare
-Trådticka
-Vedticka
-Vågbandad barkbock
-Zontaggsvamp
-Spillkråka
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 40110-2025 artfynd.xlsx", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 40110-2025 karta.png", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 40110-2025 georefererad karta.tif", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="Z2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 40110-2025 karta knärot.png", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 40110-2025 FSC-klagomål.docx", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 40110-2025 FSC-klagomål mail.docx", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 40110-2025 tillsynsbegäran.docx", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 40110-2025 tillsynsbegäran mail.docx", "A 40110-2025")</f>
-        <v/>
-      </c>
-      <c r="AE2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 40110-2025 prioriterade fågelarter.docx", "A 40110-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 24264-2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>16</v>
-      </c>
-      <c r="T3" t="n">
-        <v>28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>28</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Motaggsvamp
@@ -816,111 +672,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24264-2023 artfynd.xlsx", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24264-2023 karta.png", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24264-2023 georefererad karta.tif", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24264-2023 FSC-klagomål.docx", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24264-2023 FSC-klagomål mail.docx", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24264-2023 tillsynsbegäran.docx", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24264-2023 tillsynsbegäran mail.docx", "A 24264-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24264-2023 prioriterade fågelarter.docx", "A 24264-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>A 24365-2023</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D3" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E3" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L3" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>7</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>11</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T3" t="n">
         <v>14</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U3" t="n">
         <v>14</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Kortskaftad ärgspik
@@ -935,116 +791,116 @@
 Jättesvampmal</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24365-2023 artfynd.xlsx", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24365-2023 karta.png", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24365-2023 georefererad karta.tif", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24365-2023 FSC-klagomål.docx", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24365-2023 FSC-klagomål mail.docx", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24365-2023 tillsynsbegäran.docx", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24365-2023 tillsynsbegäran mail.docx", "A 24365-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24365-2023 prioriterade fågelarter.docx", "A 24365-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 52259-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>45608</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E4" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I4" t="n">
         <v>11.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>7</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T4" t="n">
         <v>9</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U4" t="n">
         <v>8</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1055,116 +911,116 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 52259-2024 artfynd.xlsx", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 52259-2024 karta.png", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 52259-2024 georefererad karta.tif", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 52259-2024 FSC-klagomål.docx", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 52259-2024 FSC-klagomål mail.docx", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 52259-2024 tillsynsbegäran.docx", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 52259-2024 tillsynsbegäran mail.docx", "A 52259-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 52259-2024 prioriterade fågelarter.docx", "A 52259-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A 49419-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D5" s="1" t="n">
         <v>45211</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I5" t="n">
         <v>1.9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J5" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>6</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T5" t="n">
         <v>7</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U5" t="n">
         <v>7</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ladusvala
@@ -1174,116 +1030,116 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49419-2023 artfynd.xlsx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49419-2023 karta.png", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49419-2023 georefererad karta.tif", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49419-2023 FSC-klagomål.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49419-2023 FSC-klagomål mail.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49419-2023 tillsynsbegäran.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49419-2023 tillsynsbegäran mail.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49419-2023 prioriterade fågelarter.docx", "A 49419-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 49421-2023</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>45211</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I6" t="n">
         <v>1.4</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Sexfläckig bastardsvärmare
@@ -1293,116 +1149,116 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49421-2023 artfynd.xlsx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49421-2023 karta.png", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49421-2023 georefererad karta.tif", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49421-2023 FSC-klagomål.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49421-2023 FSC-klagomål mail.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49421-2023 tillsynsbegäran.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49421-2023 tillsynsbegäran mail.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49421-2023 prioriterade fågelarter.docx", "A 49421-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31651-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tallticka
@@ -1411,39 +1267,151 @@
 Blåsippa</t>
         </is>
       </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31651-2026 artfynd.xlsx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32508-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44782</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Strutbräken
+Blåsippa
+Kopparödla</t>
+        </is>
+      </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31651-2026 artfynd.xlsx", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 32508-2022 artfynd.xlsx", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 32508-2022 karta.png", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 32508-2022 georefererad karta.tif", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 32508-2022 FSC-klagomål.docx", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 32508-2022 FSC-klagomål mail.docx", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 32508-2022 tillsynsbegäran.docx", "A 32508-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 32508-2022 tillsynsbegäran mail.docx", "A 32508-2022")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32508-2022</t>
+          <t>A 24254-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1453,14 +1421,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44782</v>
+        <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,28 +1440,23 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1502,60 +1465,60 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken
-Blåsippa
-Kopparödla</t>
+          <t>Tallharticka
+Kandelabersvamp
+Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 32508-2022 artfynd.xlsx", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 32508-2022 karta.png", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 32508-2022 georefererad karta.tif", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 32508-2022 FSC-klagomål.docx", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 32508-2022 FSC-klagomål mail.docx", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 32508-2022 tillsynsbegäran.docx", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 32508-2022 tillsynsbegäran mail.docx", "A 32508-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24254-2023</t>
+          <t>A 24384-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1572,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1585,10 +1548,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1600,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1609,60 +1572,64 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tallharticka
-Kandelabersvamp
-Vit vedfingersvamp</t>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24384-2023</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1676,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45076</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1719,54 +1686,54 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
@@ -1790,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1897,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1992,7 +1959,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2006,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45415</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2022,7 +1989,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2034,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2046,57 +2013,52 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2120,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2320,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2337,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2350,13 +2312,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2380,53 +2342,52 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2443,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2496,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2561,16 +2522,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2585,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2601,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2653,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2671,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2711,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2763,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2781,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2814,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2873,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2891,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2924,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2983,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3076,7 +3037,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3093,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,16 +3067,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3130,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3146,42 +3107,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3195,10 +3156,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3172,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3220,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3235,58 +3196,26 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3300,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3245,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3359,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3373,10 +3302,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3388,8 +3317,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3432,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3446,10 +3380,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44771</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,8 +3395,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3505,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3519,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3540,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3579,11 +3518,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3600,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3618,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3658,10 +3621,10 @@
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3671,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3690,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3735,108 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 31651-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1683,283 +1683,283 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,21 +2094,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2119,59 +2124,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,14 +2186,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2200,25 +2205,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,14 +2521,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2555,49 +2560,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,7 +2637,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2665,49 +2670,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2717,14 +2722,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,13 +2741,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2786,38 +2786,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,13 +3317,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3371,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3474,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,35 +3513,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,7 +3534,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3609,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31632-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,14 +1746,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46223</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1765,13 +1765,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1783,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1795,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1807,159 +1802,164 @@
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,16 +2094,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2112,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2124,59 +2119,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2186,14 +2181,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,20 +2200,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,19 +2521,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2560,49 +2555,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2637,7 +2632,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2670,49 +2665,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2722,14 +2717,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,8 +2736,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2786,38 +2786,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>46225</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,8 +3317,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3435,6 +3440,30 @@
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -3456,7 +3485,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3527,14 +3556,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3609,10 +3638,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24254-2023</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45076</v>
+        <v>45415</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,367 +1480,367 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24254-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallharticka
 Kandelabersvamp
 Vit vedfingersvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 24384-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 25210-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46175</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>0.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2122,49 +2122,49 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2624,21 +2624,16 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2665,42 +2660,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
@@ -2724,7 +2719,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2829,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2922,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2941,10 +2936,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2957,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2995,49 +2990,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3047,14 +3042,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,17 +3061,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3103,46 +3103,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45813</v>
+        <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,13 +3317,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3371,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46223</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3440,30 +3435,6 @@
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -3485,7 +3456,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3546,7 +3517,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3556,14 +3527,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3609,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 24254-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45415</v>
+        <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,22 +1441,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,260 +1480,260 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallharticka
+Kandelabersvamp
+Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24254-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallharticka
-Kandelabersvamp
-Vit vedfingersvamp</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2122,49 +2122,49 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2667,42 +2667,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,7 +2719,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2777,42 +2777,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2847,13 +2847,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2880,49 +2880,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,7 +2939,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2990,42 +2990,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,8 +3244,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3305,7 +3310,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3474,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3513,11 +3518,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3534,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3605,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24254-2023</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45076</v>
+        <v>45415</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,260 +1480,260 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24254-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallharticka
 Kandelabersvamp
 Vit vedfingersvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 24384-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2667,42 +2667,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,7 +2719,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2777,42 +2777,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2847,13 +2847,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2880,49 +2880,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,7 +2939,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2990,42 +2990,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44798</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,13 +3244,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3310,7 +3305,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3371,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3474,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,35 +3513,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,7 +3534,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3634,14 +3605,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45813</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45415</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45415</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 24254-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45415</v>
+        <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,22 +1441,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,486 +1480,486 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallharticka
+Kandelabersvamp
+Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24254-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallharticka
-Kandelabersvamp
-Vit vedfingersvamp</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,21 +2094,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2119,59 +2124,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,14 +2186,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2200,25 +2205,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,52 +2230,52 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,17 +2521,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2555,49 +2560,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2607,14 +2612,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,8 +2631,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2660,10 +2670,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2671,38 +2681,38 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,7 +2729,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,13 +2747,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2770,49 +2780,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2826,10 +2836,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2847,7 +2857,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2887,42 +2897,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2932,14 +2942,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2949,21 +2959,16 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2990,49 +2995,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3042,14 +3047,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,13 +3066,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3111,38 +3111,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44852</v>
+        <v>46225</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3171,8 +3171,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3225,14 +3230,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45813</v>
+        <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,8 +3249,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3284,11 +3294,35 @@
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3302,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>46225</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,8 +3351,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3361,7 +3400,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3375,10 +3414,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3390,13 +3429,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3439,7 +3473,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3449,14 +3483,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3468,13 +3502,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3517,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3527,14 +3556,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3609,10 +3638,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 24384-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1581,267 +1581,267 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>0.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>45415</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,35 +2352,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2567,42 +2567,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2670,49 +2670,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,19 +2741,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2783,46 +2778,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2836,10 +2831,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2890,49 +2885,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2942,14 +2937,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,14 +2956,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2998,46 +2998,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3107,42 +3107,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46225</v>
+        <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3169,11 +3169,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -3220,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3230,14 +3225,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46223</v>
+        <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3249,13 +3244,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3294,35 +3284,11 @@
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3302,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3351,13 +3317,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3400,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3414,10 +3375,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3429,8 +3390,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3473,7 +3439,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3483,14 +3449,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44852</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3502,8 +3468,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3546,7 +3517,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3556,14 +3527,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3609,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24254-2023</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45076</v>
+        <v>45415</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,486 +1480,486 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24254-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallharticka
 Kandelabersvamp
 Vit vedfingersvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 24384-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 25210-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46175</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>0.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,16 +2094,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2112,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2124,59 +2119,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2186,14 +2181,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,20 +2200,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,13 +2521,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2560,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2571,38 +2566,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2637,7 +2632,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2670,49 +2665,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2722,14 +2717,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,8 +2736,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2786,38 +2786,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,8 +3317,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3474,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3513,11 +3518,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3534,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3609,10 +3638,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 24254-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45415</v>
+        <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,22 +1441,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1480,486 +1480,486 @@
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallharticka
+Kandelabersvamp
+Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24254-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallharticka
-Kandelabersvamp
-Vit vedfingersvamp</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2122,49 +2122,49 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,35 +2457,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2672,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2775,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,13 +3317,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3371,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3474,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,35 +3513,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,7 +3534,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3609,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1683,283 +1683,283 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2122,49 +2122,49 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2672,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2775,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45813</v>
+        <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,8 +3244,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3305,7 +3310,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3474,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3513,11 +3518,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3534,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3605,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1683,283 +1683,283 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,21 +2094,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2119,59 +2124,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,14 +2186,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2200,25 +2205,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,52 +2230,52 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2672,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2775,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,13 +3244,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3293,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3303,14 +3298,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3322,8 +3317,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,35 +3518,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3560,10 +3536,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3557,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3620,6 +3596,30 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 17467-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46175</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1683,283 +1683,283 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,16 +2094,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2112,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2124,59 +2119,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2186,14 +2181,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,20 +2200,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,52 +2230,52 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2672,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2775,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44852</v>
+        <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44771</v>
+        <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3440,11 +3440,35 @@
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3461,7 +3485,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3503,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3522,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3532,14 +3556,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46223</v>
+        <v>44798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3557,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3596,35 +3620,11 @@
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45813</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17467-2024</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1683,283 +1683,283 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,21 +2094,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2119,59 +2124,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,14 +2186,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2200,25 +2205,20 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2562,42 +2562,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2672,42 +2672,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2775,49 +2775,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,42 +2885,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,13 +3317,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3371,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46223</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3440,30 +3435,6 @@
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -3485,7 +3456,7 @@
         <v>46225</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3546,7 +3517,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3556,14 +3527,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3552,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3609,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3624,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3669,30 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24384-2023</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1581,267 +1581,267 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>45415</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,42 +2352,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2457,42 +2457,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2519,16 +2519,21 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2555,42 +2560,42 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2724,7 +2729,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2822,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2831,10 +2836,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,7 +2857,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2885,49 +2890,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2937,14 +2942,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,19 +2961,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2998,46 +2998,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3107,35 +3107,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,8 +3244,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3305,7 +3310,7 @@
         <v>44771</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3474,7 +3479,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3513,11 +3518,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3534,7 +3563,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3581,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3595,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3605,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>44852</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3624,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3669,30 +3693,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24254-2023</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,22 +1441,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1465,501 +1465,501 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 24254-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallharticka
 Kandelabersvamp
 Vit vedfingersvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D13" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2016,56 +2016,56 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,16 +2094,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2112,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2124,59 +2119,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2186,14 +2181,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,20 +2200,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,35 +2352,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2509,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2567,42 +2567,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2670,49 +2670,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2729,7 +2729,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2780,42 +2780,42 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
         <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2949,7 +2949,7 @@
         <v>45076</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3002,42 +3002,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3107,42 +3107,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45813</v>
+        <v>46225</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3171,8 +3171,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3225,14 +3230,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44798</v>
+        <v>46225</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3255,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3293,7 +3298,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3307,10 +3312,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44771</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3322,8 +3327,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3362,11 +3372,35 @@
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr"/>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,14 +3410,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3393,11 +3427,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3444,7 +3473,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3454,14 +3483,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3473,13 +3502,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3518,35 +3542,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46225</v>
+        <v>44771</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3575,13 +3575,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3624,7 +3619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,10 +3633,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44852</v>
+        <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3648,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45076</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45076</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45076</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>46225</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46225</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44771</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45076</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45076</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45076</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>46225</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46225</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44771</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>44782</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 24254-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1441,518 +1441,518 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallharticka
+Kandelabersvamp
+Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>14</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24254-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallharticka
-Kandelabersvamp
-Vit vedfingersvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
         <v>45076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,21 +2094,26 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2119,59 +2124,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,14 +2186,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2200,16 +2205,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2230,59 +2230,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2352,35 +2352,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,13 +2521,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2560,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -2571,38 +2566,38 @@
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,7 +2614,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2637,7 +2632,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2670,49 +2665,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2729,7 +2724,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,13 +2742,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2787,42 +2782,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2836,10 +2831,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2852,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2897,42 +2892,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2942,14 +2937,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,8 +2956,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -3006,38 +3006,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,7 +3054,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3107,42 +3107,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46225</v>
+        <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3171,13 +3171,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3237,7 +3232,7 @@
         <v>46225</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3310,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3400,7 +3395,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3410,14 +3405,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45813</v>
+        <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3429,8 +3424,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3556,14 +3556,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3575,8 +3575,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3619,7 +3624,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3629,14 +3634,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3648,13 +3653,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE31"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45211</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32508-2022</t>
+          <t>A 44802-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44782</v>
+        <v>46318</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1364,701 +1364,709 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blodvaxing
+Gulvaxing
+Hagfingersvamp
+Mönjevaxing
+Papegojvaxing</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 44802-2026 artfynd.xlsx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 44802-2026 karta.png", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 44802-2026 georefererad karta.tif", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 44802-2026 FSC-klagomål.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 44802-2026 FSC-klagomål mail.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 44802-2026 tillsynsbegäran.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 44802-2026 tillsynsbegäran mail.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 32508-2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44782</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Strutbräken
 Blåsippa
 Kopparödla</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 32508-2022 artfynd.xlsx", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 32508-2022 karta.png", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 32508-2022 georefererad karta.tif", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 32508-2022 FSC-klagomål.docx", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 32508-2022 FSC-klagomål mail.docx", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 32508-2022 tillsynsbegäran.docx", "A 32508-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 32508-2022 tillsynsbegäran mail.docx", "A 32508-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 24254-2023</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.2</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallharticka
 Kandelabersvamp
 Vit vedfingersvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24254-2023 artfynd.xlsx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24254-2023 karta.png", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24254-2023 georefererad karta.tif", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24254-2023 FSC-klagomål.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24254-2023 FSC-klagomål mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24254-2023 tillsynsbegäran.docx", "A 24254-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24254-2023 tillsynsbegäran mail.docx", "A 24254-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 24384-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45076</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D14" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 24368-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Plattlummer</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
@@ -2082,7 +2090,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2184,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2190,10 +2198,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,19 +2214,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2233,56 +2241,56 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2296,10 +2304,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2312,19 +2320,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2339,55 +2347,56 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2404,7 +2413,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,16 +2426,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2441,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2457,42 +2466,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2509,7 +2518,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,16 +2531,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2562,42 +2571,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2607,14 +2616,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,22 +2635,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2656,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2665,42 +2669,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
@@ -2724,7 +2728,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2838,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2931,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2941,10 +2945,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2966,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2995,49 +2999,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3047,14 +3051,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,8 +3070,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3103,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3111,38 +3120,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3156,10 +3165,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45813</v>
+        <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3172,13 +3181,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3202,20 +3211,52 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3225,14 +3266,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46225</v>
+        <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3244,13 +3285,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3293,7 +3329,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3307,10 +3343,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3328,7 +3364,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3367,35 +3403,11 @@
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr"/>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3412,7 +3424,7 @@
         <v>46225</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3430,7 +3442,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3473,7 +3485,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3483,14 +3495,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44852</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3502,8 +3514,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3542,11 +3559,35 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3556,14 +3597,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44798</v>
+        <v>44771</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3575,13 +3616,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3621,10 +3657,10 @@
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3634,14 +3670,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44771</v>
+        <v>44798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3653,8 +3689,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3693,6 +3734,79 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 27561-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45813</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49419-2023</t>
+          <t>A 49421-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1006,21 +1006,140 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
         <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
       </c>
       <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Sexfläckig bastardsvärmare
+Gulsparv
+Tallticka
+Mindre märgborre
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49421-2023 artfynd.xlsx", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49421-2023 karta.png", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49421-2023 georefererad karta.tif", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49421-2023 FSC-klagomål.docx", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49421-2023 FSC-klagomål mail.docx", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49421-2023 tillsynsbegäran.docx", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49421-2023 tillsynsbegäran mail.docx", "A 49421-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49421-2023 prioriterade fågelarter.docx", "A 49421-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49419-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>7</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ladusvala
@@ -1030,155 +1149,36 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49419-2023 artfynd.xlsx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49419-2023 karta.png", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49419-2023 georefererad karta.tif", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49419-2023 FSC-klagomål.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49419-2023 FSC-klagomål mail.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49419-2023 tillsynsbegäran.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49419-2023 tillsynsbegäran mail.docx", "A 49419-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49419-2023 prioriterade fågelarter.docx", "A 49419-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49421-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Sexfläckig bastardsvärmare
-Gulsparv
-Tallticka
-Mindre märgborre
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49421-2023 artfynd.xlsx", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49421-2023 karta.png", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49421-2023 georefererad karta.tif", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49421-2023 FSC-klagomål.docx", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49421-2023 FSC-klagomål mail.docx", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49421-2023 tillsynsbegäran.docx", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49421-2023 tillsynsbegäran mail.docx", "A 49421-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49421-2023 prioriterade fågelarter.docx", "A 49421-2023")</f>
         <v/>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46318</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24384-2023</t>
+          <t>A 25210-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45076</v>
+        <v>46175</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1695,385 +1695,385 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31632-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Mindre märgborre
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 24384-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45076</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kolflarnlav
 Vedskivlav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 17467-2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45415</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>14</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 31632-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Mindre märgborre
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 25210-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,16 +2102,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2120,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2132,59 +2127,59 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2194,14 +2189,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2213,20 +2208,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2238,59 +2238,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2347,56 +2347,56 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 24257-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2413,7 +2413,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,16 +2426,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2466,42 +2466,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24257-2023</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2518,7 +2518,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2571,42 +2571,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24257-2023 artfynd.xlsx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24257-2023 karta.png", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24257-2023 georefererad karta.tif", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24257-2023 FSC-klagomål.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24257-2023 FSC-klagomål mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24257-2023 tillsynsbegäran.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24257-2023 tillsynsbegäran mail.docx", "A 24257-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2635,17 +2635,22 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2660,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2669,42 +2674,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
@@ -2728,7 +2733,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2843,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2936,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2971,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2999,49 +3004,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3051,14 +3056,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3070,19 +3075,14 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3112,46 +3112,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3168,7 +3168,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3221,35 +3221,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31650-2026</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46225</v>
+        <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3358,13 +3358,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3407,7 +3402,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31645-2026</t>
+          <t>A 35404-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3417,14 +3412,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46225</v>
+        <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3437,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3485,7 +3480,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31246-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>44771</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3514,13 +3509,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3559,35 +3549,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31246-2022</t>
+          <t>A 31645-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3601,10 +3567,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44771</v>
+        <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3616,8 +3582,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3660,7 +3631,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35404-2022</t>
+          <t>A 31651-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3670,14 +3641,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44798</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3695,7 +3666,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3734,11 +3705,35 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3748,14 +3743,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45813</v>
+        <v>46225</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3767,8 +3762,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HUDDINGE.xlsx
+++ b/Översikt HUDDINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45076</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45076</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45608</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49421-2023</t>
+          <t>A 49419-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +964,7 @@
         <v>45211</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,45 +982,164 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ladusvala
+Fiskgjuse
+Havsörn
+Kråka
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49419-2023 artfynd.xlsx", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49419-2023 karta.png", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49419-2023 georefererad karta.tif", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49419-2023 FSC-klagomål.docx", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49419-2023 FSC-klagomål mail.docx", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49419-2023 tillsynsbegäran.docx", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49419-2023 tillsynsbegäran mail.docx", "A 49419-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49419-2023 prioriterade fågelarter.docx", "A 49419-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 49421-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Sexfläckig bastardsvärmare
@@ -1030,162 +1149,43 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49421-2023 artfynd.xlsx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49421-2023 karta.png", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49421-2023 georefererad karta.tif", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49421-2023 FSC-klagomål.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49421-2023 FSC-klagomål mail.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49421-2023 tillsynsbegäran.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49421-2023 tillsynsbegäran mail.docx", "A 49421-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49421-2023 prioriterade fågelarter.docx", "A 49421-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 49419-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>7</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ladusvala
-Fiskgjuse
-Havsörn
-Kråka
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 49419-2023 artfynd.xlsx", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 49419-2023 karta.png", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 49419-2023 georefererad karta.tif", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 49419-2023 FSC-klagomål.docx", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 49419-2023 FSC-klagomål mail.docx", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 49419-2023 tillsynsbegäran.docx", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 49419-2023 tillsynsbegäran mail.docx", "A 49419-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 49419-2023 prioriterade fågelarter.docx", "A 49419-2023")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 44802-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46223</v>
+        <v>46318</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1244,21 +1244,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blodvaxing
+Gulvaxing
+Hagfingersvamp
+Mönjevaxing
+Papegojvaxing</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 44802-2026 artfynd.xlsx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 44802-2026 karta.png", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 44802-2026 georefererad karta.tif", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 44802-2026 FSC-klagomål.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 44802-2026 FSC-klagomål mail.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 44802-2026 tillsynsbegäran.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 44802-2026 tillsynsbegäran mail.docx", "A 44802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 31651-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tallticka
@@ -1267,146 +1381,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31651-2026 artfynd.xlsx", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 44802-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blodvaxing
-Gulvaxing
-Hagfingersvamp
-Mönjevaxing
-Papegojvaxing</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 44802-2026 artfynd.xlsx", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 44802-2026 karta.png", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 44802-2026 georefererad karta.tif", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 44802-2026 FSC-klagomål.docx", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 44802-2026 FSC-klagomål mail.docx", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 44802-2026 tillsynsbegäran.docx", "A 44802-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 44802-2026 tillsynsbegäran mail.docx", "A 44802-2026")</f>
         <v/>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         <v>44782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25210-2026</t>
+          <t>A 24384-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1695,385 +1695,385 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17467-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25210-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HUDDINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Mindre vattensalamander
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25210-2026 artfynd.xlsx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25210-2026 karta.png", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25210-2026 georefererad karta.tif", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25210-2026 FSC-klagomål.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25210-2026 FSC-klagomål mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25210-2026 tillsynsbegäran.docx", "A 25210-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25210-2026 tillsynsbegäran mail.docx", "A 25210-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31632-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>0.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Mindre märgborre
 Kopparödla</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31632-2026 artfynd.xlsx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31632-2026 karta.png", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31632-2026 georefererad karta.tif", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31632-2026 FSC-klagomål.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31632-2026 FSC-klagomål mail.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31632-2026 tillsynsbegäran.docx", "A 31632-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31632-2026 tillsynsbegäran mail.docx", "A 31632-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 24384-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45076</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Vedskivlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24384-2023 artfynd.xlsx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24384-2023 karta.png", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24384-2023 georefererad karta.tif", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24384-2023 FSC-klagomål.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24384-2023 FSC-klagomål mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24384-2023 tillsynsbegäran.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24384-2023 tillsynsbegäran mail.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/fåglar/A 24384-2023 prioriterade fågelarter.docx", "A 24384-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17467-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 17467-2024 artfynd.xlsx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 17467-2024 karta.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 17467-2024 georefererad karta.tif", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/knärot/A 17467-2024 karta knärot.png", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 17467-2024 FSC-klagomål.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 17467-2024 FSC-klagomål mail.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 17467-2024 tillsynsbegäran.docx", "A 17467-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 17467-2024 tillsynsbegäran mail.docx", "A 17467-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25208-2026</t>
+          <t>A 24368-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46175</v>
+        <v>45076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2130,56 +2130,56 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knölvial
-Gullviva</t>
+          <t>Motaggsvamp
+Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31569-2026</t>
+          <t>A 25208-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2189,14 +2189,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2208,16 +2208,11 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2226,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2238,59 +2233,59 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Sexfläckig bastardsvärmare</t>
+          <t>Knölvial
+Gullviva</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 25208-2026 artfynd.xlsx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 25208-2026 karta.png", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 25208-2026 georefererad karta.tif", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 25208-2026 FSC-klagomål.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 25208-2026 FSC-klagomål mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 25208-2026 tillsynsbegäran.docx", "A 25208-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 25208-2026 tillsynsbegäran mail.docx", "A 25208-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24368-2023</t>
+          <t>A 31569-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2300,14 +2295,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2319,20 +2314,25 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2344,52 +2344,52 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Plattlummer</t>
+          <t>Mindre blåvinge
+Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24368-2023 artfynd.xlsx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31569-2026 artfynd.xlsx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24368-2023 karta.png", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31569-2026 karta.png", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24368-2023 georefererad karta.tif", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31569-2026 georefererad karta.tif", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24368-2023 FSC-klagomål.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31569-2026 FSC-klagomål.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24368-2023 FSC-klagomål mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31569-2026 FSC-klagomål mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24368-2023 tillsynsbegäran.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31569-2026 tillsynsbegäran.docx", "A 31569-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24368-2023 tillsynsbegäran mail.docx", "A 24368-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31569-2026 tillsynsbegäran mail.docx", "A 31569-2026")</f>
         <v/>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
         <v>45076</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24233-2023</t>
+          <t>A 24262-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2518,7 +2518,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2571,42 +2571,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31633-2026</t>
+          <t>A 24363-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2635,13 +2635,8 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2674,49 +2669,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31514-2026</t>
+          <t>A 24233-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2726,14 +2721,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>45076</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2745,22 +2740,17 @@
           <t>HUDDINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2775,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2784,49 +2774,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24233-2023 artfynd.xlsx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24233-2023 karta.png", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24233-2023 georefererad karta.tif", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24233-2023 FSC-klagomål.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24233-2023 FSC-klagomål mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24233-2023 tillsynsbegäran.docx", "A 24233-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24233-2023 tillsynsbegäran mail.docx", "A 24233-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31568-2026</t>
+          <t>A 31633-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2843,7 +2833,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2851,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2894,49 +2884,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31633-2026 artfynd.xlsx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31633-2026 karta.png", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31633-2026 georefererad karta.tif", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31633-2026 FSC-klagomål.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31633-2026 FSC-klagomål mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31633-2026 tillsynsbegäran.docx", "A 31633-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31633-2026 tillsynsbegäran mail.docx", "A 31633-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31795-2026</t>
+          <t>A 31514-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2950,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2971,13 +2961,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3004,49 +2994,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31514-2026 artfynd.xlsx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31514-2026 karta.png", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31514-2026 georefererad karta.tif", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31514-2026 FSC-klagomål.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31514-2026 FSC-klagomål mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31514-2026 tillsynsbegäran.docx", "A 31514-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31514-2026 tillsynsbegäran mail.docx", "A 31514-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24262-2023</t>
+          <t>A 31568-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3056,14 +3046,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45076</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,14 +3065,19 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3112,46 +3107,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24262-2023 artfynd.xlsx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31568-2026 artfynd.xlsx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24262-2023 karta.png", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31568-2026 karta.png", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24262-2023 georefererad karta.tif", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31568-2026 georefererad karta.tif", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24262-2023 FSC-klagomål.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31568-2026 FSC-klagomål.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24262-2023 FSC-klagomål mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31568-2026 FSC-klagomål mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24262-2023 tillsynsbegäran.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31568-2026 tillsynsbegäran.docx", "A 31568-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24262-2023 tillsynsbegäran mail.docx", "A 24262-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31568-2026 tillsynsbegäran mail.docx", "A 31568-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24363-2023</t>
+          <t>A 31795-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3161,14 +3156,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45076</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,8 +3175,13 @@
           <t>HUDDINGE</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3225,38 +3225,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 24363-2023 artfynd.xlsx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/artfynd/A 31795-2026 artfynd.xlsx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 24363-2023 karta.png", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31795-2026 karta.png", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 24363-2023 georefererad karta.tif", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31795-2026 georefererad karta.tif", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 24363-2023 FSC-klagomål.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31795-2026 FSC-klagomål.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 24363-2023 FSC-klagomål mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31795-2026 FSC-klagomål mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 24363-2023 tillsynsbegäran.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31795-2026 tillsynsbegäran.docx", "A 31795-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 24363-2023 tillsynsbegäran mail.docx", "A 24363-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31795-2026 tillsynsbegäran mail.docx", "A 31795-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47173-2022</t>
+          <t>A 27561-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27561-2025</t>
+          <t>A 47173-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45813</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>44798</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44771</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>46225</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31651-2026</t>
+          <t>A 31650-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3705,108 +3705,6 @@
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor/A 31651-2026 karta.png", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/kartor_geotiff/A 31651-2026 georefererad karta.tif", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomål/A 31651-2026 FSC-klagomål.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/klagomålsmail/A 31651-2026 FSC-klagomål mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsyn/A 31651-2026 tillsynsbegäran.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0126/tillsynsmail/A 31651-2026 tillsynsbegäran mail.docx", "A 31651-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 31650-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>HUDDINGE</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
